--- a/data/trans_dic/IP12B$otros-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor</t>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,52</t>
+          <t>0,0; 58,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,04</t>
+          <t>0,0; 40,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 43,8</t>
+          <t>5,64; 47,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 38,04</t>
+          <t>4,51; 37,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 28,41</t>
+          <t>2,92; 27,28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,63</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 38,39</t>
+          <t>5,07; 37,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,51</t>
+          <t>0,0; 22,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 57,13</t>
+          <t>7,77; 56,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,21</t>
+          <t>0,0; 24,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 21,57</t>
+          <t>2,4; 21,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 28,9</t>
+          <t>3,53; 26,88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,15</t>
+          <t>0,0; 57,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,87</t>
+          <t>0,0; 80,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,5</t>
+          <t>0,0; 51,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,21</t>
+          <t>0,0; 43,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 45,42</t>
+          <t>5,75; 43,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,47</t>
+          <t>0,0; 48,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,22</t>
+          <t>0,0; 48,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 61,45</t>
+          <t>8,23; 56,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,7</t>
+          <t>7,75; 59,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 42,77</t>
+          <t>8,45; 43,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,99</t>
+          <t>0,0; 26,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 33,62</t>
+          <t>4,39; 33,83</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,72</t>
+          <t>0,0; 55,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,25</t>
+          <t>0,0; 42,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,91</t>
+          <t>0,0; 29,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,87</t>
+          <t>0,0; 39,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,27 +1228,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,9</t>
+          <t>0,0; 55,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 81,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,33</t>
+          <t>0,0; 56,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1257,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,93</t>
+          <t>0,0; 41,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,58</t>
+          <t>0,0; 41,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1274,7 +1275,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,79</t>
+          <t>0,0; 55,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,82</t>
+          <t>0,0; 41,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,41</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,34</t>
+          <t>0,0; 50,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,84</t>
+          <t>0,0; 28,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 40,82</t>
+          <t>4,88; 42,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,44</t>
+          <t>0,0; 26,03</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,65</t>
+          <t>0,0; 44,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,44; 46,09</t>
+          <t>9,02; 44,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,11; 44,97</t>
+          <t>9,04; 46,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,24</t>
+          <t>0,0; 31,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,8</t>
+          <t>0,0; 34,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,06; 33,97</t>
+          <t>6,4; 33,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,3; 30,35</t>
+          <t>3,28; 29,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 33,48</t>
+          <t>7,31; 31,68</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 17,89</t>
+          <t>3,06; 17,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 22,26</t>
+          <t>7,37; 22,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,56; 22,1</t>
+          <t>7,02; 23,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,09; 27,83</t>
+          <t>10,1; 26,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,43</t>
+          <t>3,88; 15,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,4; 20,65</t>
+          <t>5,61; 21,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,26</t>
+          <t>8,17; 19,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,03</t>
+          <t>7,11; 16,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 18,67</t>
+          <t>8,04; 18,16</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3324</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3179</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>571; 4815</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>614; 5129</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>564; 5267</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3979</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>616; 4576</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3128</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>622; 4559</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3927</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>625; 5707</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>609; 4629</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1634</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4647</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2514</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3760</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2676</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>880; 6656</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4157</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>810; 5582</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>633; 4866</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1236; 6326</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3922</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>856; 6604</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2512</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2699</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4324</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2482</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2916</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2500</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2869</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 1766</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2783</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4237</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2495</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3998</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2466</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2700</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3040</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3333</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>644; 5638</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2811</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2370</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3075</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1224; 6089</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1256; 6511</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3283</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3552</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1261; 6587</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>565; 5088</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1742; 7552</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>11878</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>13589</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>12830</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1344; 7551</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4517; 13485</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3871; 12972</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>4716; 12604</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2467; 9817</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2686; 10056</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>7404; 17859</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>8877; 20553</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>8280; 18700</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$otros-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,03</t>
+          <t>0,0; 57,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,28</t>
+          <t>0,0; 40,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 47,51</t>
+          <t>5,76; 46,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 37,66</t>
+          <t>4,35; 35,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 27,28</t>
+          <t>2,98; 28,4</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>0,0; 38,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 37,7</t>
+          <t>5,09; 38,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,49</t>
+          <t>0,0; 18,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 56,94</t>
+          <t>7,72; 49,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,35</t>
+          <t>0,0; 24,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 21,91</t>
+          <t>2,46; 22,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 26,88</t>
+          <t>3,56; 28,44</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,93</t>
+          <t>0,0; 50,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,65</t>
+          <t>0,0; 56,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,44</t>
+          <t>0,0; 45,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 43,5</t>
+          <t>5,96; 43,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,22 +1008,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,72</t>
+          <t>0,0; 56,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,7</t>
+          <t>0,0; 45,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 56,72</t>
+          <t>8,43; 59,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 59,54</t>
+          <t>7,39; 57,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 43,26</t>
+          <t>8,25; 43,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,35</t>
+          <t>0,0; 28,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 33,83</t>
+          <t>4,26; 33,57</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,68</t>
+          <t>0,0; 41,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,38</t>
+          <t>0,0; 43,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,3</t>
+          <t>0,0; 24,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,42</t>
+          <t>0,0; 39,05</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,85</t>
+          <t>0,0; 56,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,98</t>
+          <t>0,0; 60,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,26</t>
+          <t>0,0; 49,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,31</t>
+          <t>0,0; 41,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,86</t>
+          <t>0,0; 55,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,44</t>
+          <t>0,0; 40,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,33</t>
+          <t>0,0; 50,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,7</t>
+          <t>0,0; 22,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 42,72</t>
+          <t>5,07; 42,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,03</t>
+          <t>0,0; 27,28</t>
         </is>
       </c>
     </row>
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,69</t>
+          <t>0,0; 43,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,02; 44,9</t>
+          <t>9,47; 45,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,04; 46,86</t>
+          <t>9,07; 46,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,72</t>
+          <t>0,0; 37,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,55</t>
+          <t>0,0; 32,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 33,44</t>
+          <t>6,5; 32,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 29,52</t>
+          <t>3,49; 28,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 31,68</t>
+          <t>6,06; 31,45</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,06; 17,21</t>
+          <t>3,14; 17,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,0</t>
+          <t>6,94; 21,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,02; 23,53</t>
+          <t>7,77; 22,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,1; 26,98</t>
+          <t>9,46; 28,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 15,44</t>
+          <t>3,64; 15,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 21,01</t>
+          <t>5,23; 20,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,17; 19,71</t>
+          <t>8,52; 19,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,46</t>
+          <t>7,0; 16,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,16</t>
+          <t>7,74; 18,01</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3324</t>
+          <t>0; 3316</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3179</t>
+          <t>0; 3185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>571; 4815</t>
+          <t>584; 4719</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>614; 5129</t>
+          <t>592; 4834</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>564; 5267</t>
+          <t>575; 5483</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3979</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>616; 4576</t>
+          <t>618; 4615</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3128</t>
+          <t>0; 2569</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>622; 4559</t>
+          <t>618; 3983</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3927</t>
+          <t>0; 3900</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>625; 5707</t>
+          <t>641; 5914</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>609; 4629</t>
+          <t>614; 4897</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4647</t>
+          <t>0; 4060</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3760</t>
+          <t>0; 4148</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2676</t>
+          <t>0; 2777</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>880; 6656</t>
+          <t>912; 6717</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3143</t>
+          <t>0; 3631</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4157</t>
+          <t>0; 3876</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>810; 5582</t>
+          <t>830; 5901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>633; 4866</t>
+          <t>604; 4700</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1236; 6326</t>
+          <t>1207; 6397</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 4208</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>856; 6604</t>
+          <t>832; 6555</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2512</t>
+          <t>0; 1892</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2699</t>
+          <t>0; 2787</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4324</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2482</t>
+          <t>0; 2458</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2916</t>
+          <t>0; 2933</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2869</t>
+          <t>0; 3033</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2783</t>
+          <t>0; 3308</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4237</t>
+          <t>0; 4216</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 3988</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2466</t>
+          <t>0; 2394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3040</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3333</t>
+          <t>0; 2661</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>644; 5638</t>
+          <t>669; 5600</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2811</t>
+          <t>0; 2946</t>
         </is>
       </c>
     </row>
@@ -3007,42 +3007,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3075</t>
+          <t>0; 3020</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1224; 6089</t>
+          <t>1284; 6232</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1256; 6511</t>
+          <t>1260; 6495</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 3867</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3552</t>
+          <t>0; 3325</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1261; 6587</t>
+          <t>1281; 6461</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>565; 5088</t>
+          <t>601; 4946</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1742; 7552</t>
+          <t>1446; 7498</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1344; 7551</t>
+          <t>1378; 7814</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4517; 13485</t>
+          <t>4255; 13414</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3871; 12972</t>
+          <t>4281; 12226</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4716; 12604</t>
+          <t>4420; 13198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2467; 9817</t>
+          <t>2311; 9887</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2686; 10056</t>
+          <t>2505; 9701</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7404; 17859</t>
+          <t>7715; 17813</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8877; 20553</t>
+          <t>8735; 20341</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8280; 18700</t>
+          <t>7974; 18549</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$otros-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>22,79%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,9</t>
+          <t>0,0; 40,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,48; 43,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,36</t>
+          <t>0,0; 58,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 46,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 35,49</t>
+          <t>4,4; 38,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 28,4</t>
+          <t>2,9; 28,41</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23,98%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>15,89%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>23,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 38,02</t>
+          <t>0,0; 18,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,84; 57,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,48</t>
+          <t>5,19; 38,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 49,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,18</t>
+          <t>0,0; 24,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 22,71</t>
+          <t>2,47; 21,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 28,44</t>
+          <t>3,54; 28,9</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>20,37%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 79,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,62</t>
+          <t>0,0; 57,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,97</t>
+          <t>0,0; 58,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,08</t>
+          <t>0,0; 44,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 43,9</t>
+          <t>6,02; 45,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>18,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15,3%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>30,17%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,28</t>
+          <t>0,0; 56,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 59,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 57,51</t>
+          <t>0,0; 55,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 46,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,93; 61,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 43,74</t>
+          <t>7,79; 42,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,27</t>
+          <t>0,0; 25,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 33,57</t>
+          <t>4,36; 33,62</t>
         </is>
       </c>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,75%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,94</t>
+          <t>0,0; 22,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,05</t>
+          <t>0,0; 38,87</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44,72%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>13,28%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21,37%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,42 +1228,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,17</t>
+          <t>0,0; 60,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,23</t>
+          <t>0,0; 55,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,05</t>
+          <t>0,0; 40,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,1</t>
+          <t>0,0; 40,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>22,37%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,14%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 65,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,71</t>
+          <t>0,0; 53,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,3</t>
+          <t>0,0; 54,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,91</t>
+          <t>0,0; 31,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,07; 42,43</t>
+          <t>4,99; 40,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,28</t>
+          <t>0,0; 28,44</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>16,53%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>24,43%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,11; 44,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,9</t>
+          <t>0,0; 39,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,47; 45,96</t>
+          <t>0,0; 26,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,07; 46,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,36</t>
+          <t>0,0; 43,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,34</t>
+          <t>9,44; 46,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 32,81</t>
+          <t>6,06; 33,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 28,7</t>
+          <t>3,3; 30,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,06; 31,45</t>
+          <t>6,05; 33,48</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>13,54%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>13,43%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 17,81</t>
+          <t>10,09; 27,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,89</t>
+          <t>4,05; 15,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,77; 22,18</t>
+          <t>5,4; 20,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,46; 28,26</t>
+          <t>4,07; 17,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,56</t>
+          <t>7,5; 22,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 20,27</t>
+          <t>7,56; 22,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,52; 19,67</t>
+          <t>8,27; 19,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,0; 16,29</t>
+          <t>6,88; 16,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,74; 18,01</t>
+          <t>7,72; 18,67</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,24 +1755,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,24 +1808,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1305</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3316</t>
+          <t>0; 3160</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>556; 4440</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3185</t>
+          <t>0; 3351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>584; 4719</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>592; 4834</t>
+          <t>599; 5181</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>575; 5483</t>
+          <t>559; 5483</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1929</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>618; 4615</t>
+          <t>0; 2575</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>627; 4574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3879</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2569</t>
+          <t>631; 4660</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>618; 3983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3900</t>
+          <t>0; 3905</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>641; 5914</t>
+          <t>644; 5617</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>614; 4897</t>
+          <t>610; 4978</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2134,27 +2134,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>635</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1634</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2506</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4060</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2514</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4148</t>
+          <t>0; 4664</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2777</t>
+          <t>0; 2723</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>912; 6717</t>
+          <t>921; 6950</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1174</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2969</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3631</t>
+          <t>0; 4634</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>830; 5901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>604; 4700</t>
+          <t>0; 3578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3946</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>879; 6047</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1207; 6397</t>
+          <t>1139; 6255</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 3869</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>832; 6555</t>
+          <t>851; 6564</t>
         </is>
       </c>
     </row>
@@ -2412,27 +2412,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2465,27 +2465,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>575</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3392</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1892</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2513</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3681</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2458</t>
+          <t>0; 2447</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>659</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>694</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,42 +2676,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2466</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2933</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2500</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3033</t>
+          <t>0; 2919</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1766</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3308</t>
+          <t>0; 2761</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4216</t>
+          <t>0; 4162</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>1602</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>544</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2645</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3988</t>
+          <t>0; 3222</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2394</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2700</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3038</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2429</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2661</t>
+          <t>0; 3698</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>669; 5600</t>
+          <t>658; 5387</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2946</t>
+          <t>0; 3071</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>1137</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3313</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1266; 6247</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3020</t>
+          <t>0; 4062</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1284; 6232</t>
+          <t>0; 2755</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1260; 6495</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3325</t>
+          <t>1281; 6250</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1281; 6461</t>
+          <t>1194; 6691</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>601; 4946</t>
+          <t>570; 5229</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1446; 7498</t>
+          <t>1442; 7981</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>3772</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>8301</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>7401</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>8106</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>5429</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1378; 7814</t>
+          <t>4714; 12997</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4255; 13414</t>
+          <t>2571; 9810</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4281; 12226</t>
+          <t>2585; 9882</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4420; 13198</t>
+          <t>1786; 7849</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2311; 9887</t>
+          <t>4596; 13643</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2505; 9701</t>
+          <t>4168; 12183</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7715; 17813</t>
+          <t>7496; 17444</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>8735; 20341</t>
+          <t>8587; 20013</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7974; 18549</t>
+          <t>7951; 19226</t>
         </is>
       </c>
     </row>
